--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/ RETROVISOR 10_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/ RETROVISOR 10_02.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RR PAR RIIE BMW GS650 360 ROSCA RT0037</t>
+          <t>RETROVISOR PAR RIIE BMW GS650 360 ROSCA RT0037</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RR  RIIE BMW GS650 800 HASTE LONGA RT0039</t>
+          <t>RETROVISOR RIIE BMW GS650 800 HASTE LONGA RT0039</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RR IRON CG125 150 160 2014 A 2017 352396</t>
+          <t>RETROVISORIRON CG125 150 160 2014 A 2017 352396</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RR AWA FAZER150 2015 514</t>
+          <t>RETROVISOR AWA FAZER150 2015 514</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RR PAR EXTREMO CG TITAN FAN160cc 2014 002663</t>
+          <t>RETROVISORPAR EXTREMO CG TITAN FAN160cc 2014 002663</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RR EXTREMO FAZER YS150 2015/ NEO125/ NMAX </t>
+          <t xml:space="preserve">RETROVISOR EXTREMO FAZER YS150 2015/ NEO125/ NMAX </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RR PAR DAGOSTIN BIZ125/ BROS 2009 025451</t>
+          <t>RETROVISOR PAR DAGOSTIN BIZ125/ BROS 2009 025451</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RR DAGOSTIN TITAN KS/ES PAR 012299</t>
+          <t>RETROVISOR DAGOSTIN TITAN KS/ES PAR 012299</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RR EXTREMO BIZ125/ BROS 2009 015661</t>
+          <t>RETROVISOR EXTREMO BIZ125/ BROS 2009 015661</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RR RIIE PAR MT03 07 09 ASTE LNGA ROSCA RT0035</t>
+          <t>RETROVISORRIIE PAR MT03 07 09 ASTE LNGA ROSCA RT0035</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RR DMA PAR  MT03 07 09 ASTE LONGA ROSCA RT0035</t>
+          <t>RETROVISORDMA PAR  MT03 07 09 ASTE LONGA ROSCA RT0035</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RR MINI GVS FAZER YS150 PAR 4166</t>
+          <t>RETROVISOR MINI GVS FAZER YS150 PAR 4166</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/ RETROVISOR 10_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/ RETROVISOR 10_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -499,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RETROVISORIRON CG125 150 160 2014 A 2017 352396</t>
+          <t>RETROVISOR IRON CG125 150 160 2014 A 2017 352396</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -507,7 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -528,7 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,7 +524,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RETROVISORPAR EXTREMO CG TITAN FAN160cc 2014 002663</t>
+          <t>RETROVISOR PAR EXTREMO CG TITAN FAN160cc 2014 002663</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -549,7 +532,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -570,7 +552,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -591,7 +572,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -612,7 +592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -633,7 +612,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -646,7 +624,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RETROVISORRIIE PAR MT03 07 09 ASTE LNGA ROSCA RT0035</t>
+          <t xml:space="preserve">RETROVISOR RIIE PAR MT03 07 09 ASTE LNGA ROSCA RT0035  </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -654,7 +632,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -667,7 +644,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RETROVISORDMA PAR  MT03 07 09 ASTE LONGA ROSCA RT0035</t>
+          <t>RETROVISOR DMA PAR  MT03 07 09 ASTE LONGA ROSCA RT0035</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -675,7 +652,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -696,7 +672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -709,7 +684,6 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
